--- a/Extraction/Master/standard_coa_master.xlsx
+++ b/Extraction/Master/standard_coa_master.xlsx
@@ -1,36 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janarddanm\Downloads\01-09-2026\PFG_Extraction\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4196E34-FBA0-469C-BD6F-CFC61906AE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="5430"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$E$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$187</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="206">
   <si>
     <t>Sector</t>
   </si>
@@ -134,9 +127,18 @@
     <t>Total Capital Assets</t>
   </si>
   <si>
+    <t>Total Restricted Assets</t>
+  </si>
+  <si>
     <t>Total Noncurrent Assets</t>
   </si>
   <si>
+    <t>PROP_SNP</t>
+  </si>
+  <si>
+    <t>Net Capital Assets</t>
+  </si>
+  <si>
     <t>Deferred Outflows of Resources</t>
   </si>
   <si>
@@ -245,6 +247,9 @@
     <t>Total Liabilities, Deferred inflows of resources, and Net position</t>
   </si>
   <si>
+    <t>Other Net Position</t>
+  </si>
+  <si>
     <t>Fund Balances</t>
   </si>
   <si>
@@ -434,6 +439,12 @@
     <t>Net Change In Fund Balances</t>
   </si>
   <si>
+    <t>Fund Balance - Beginning of Year</t>
+  </si>
+  <si>
+    <t>Fund Balance - End of Year</t>
+  </si>
+  <si>
     <t>PROP_IS</t>
   </si>
   <si>
@@ -470,6 +481,15 @@
     <t>Change In Net Position</t>
   </si>
   <si>
+    <t>Change in Net Position</t>
+  </si>
+  <si>
+    <t>Net Position - Beginning of Year</t>
+  </si>
+  <si>
+    <t>Net Position - End of Year</t>
+  </si>
+  <si>
     <t>PROP_CFS</t>
   </si>
   <si>
@@ -509,6 +529,21 @@
     <t>Total Balance of Cash and Cash Equivalents</t>
   </si>
   <si>
+    <t>Net Change in Cash and Cash Equivalents</t>
+  </si>
+  <si>
+    <t>Reconciliation of Operating Income (Loss)</t>
+  </si>
+  <si>
+    <t>Reconciliation Item</t>
+  </si>
+  <si>
+    <t>Non-cash Activities</t>
+  </si>
+  <si>
+    <t>Non-cash Items</t>
+  </si>
+  <si>
     <t>Program Expenses - Business-type Activities</t>
   </si>
   <si>
@@ -516,19 +551,103 @@
   </si>
   <si>
     <t>Changes in Net Position</t>
+  </si>
+  <si>
+    <t>CAPITAL_ASSETS</t>
+  </si>
+  <si>
+    <t>Governmental Activities</t>
+  </si>
+  <si>
+    <t>Depreciable Assets</t>
+  </si>
+  <si>
+    <t>Non-depreciable Assets</t>
+  </si>
+  <si>
+    <t>Construction-in-Progress</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation</t>
+  </si>
+  <si>
+    <t>Total Non-depreciable Assets</t>
+  </si>
+  <si>
+    <t>Total Depreciable Assets</t>
+  </si>
+  <si>
+    <t>Total Accumulated Depreciation</t>
+  </si>
+  <si>
+    <t>Total Capital Asset</t>
+  </si>
+  <si>
+    <t>Business-type Activities</t>
+  </si>
+  <si>
+    <t>Component Units</t>
+  </si>
+  <si>
+    <t>TAX_BASE</t>
+  </si>
+  <si>
+    <t>Assessed Value</t>
+  </si>
+  <si>
+    <t>Year Type</t>
+  </si>
+  <si>
+    <t>Full Value</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Levy</t>
+  </si>
+  <si>
+    <t>% Current Collected</t>
+  </si>
+  <si>
+    <t>% Total Collected</t>
+  </si>
+  <si>
+    <t>DEBT</t>
+  </si>
+  <si>
+    <t>Long-term Debt</t>
+  </si>
+  <si>
+    <t>Short-term Debt</t>
+  </si>
+  <si>
+    <t>State Loan</t>
+  </si>
+  <si>
+    <t>Lease Liability</t>
+  </si>
+  <si>
+    <t>Premium/ Discount</t>
+  </si>
+  <si>
+    <t>Pension-OPEB Liability</t>
+  </si>
+  <si>
+    <t>Short-term Liability</t>
+  </si>
+  <si>
+    <t>Long-term Liability</t>
+  </si>
+  <si>
+    <t>Total long-term obligations</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,152 +663,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,194 +683,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -903,253 +692,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1160,62 +707,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1473,18 +977,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E186"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E269"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="11.7619047619048" customWidth="1"/>
-    <col min="4" max="4" width="8.18095238095238" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="50.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1505,7 +1009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1794,7 +1298,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -1811,7 +1315,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -1828,7 +1332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:5">
+    <row r="21" spans="1:5" s="6" customFormat="1">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -1845,7 +1349,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:5">
+    <row r="22" spans="1:5" s="6" customFormat="1">
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
@@ -1862,7 +1366,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:5">
+    <row r="23" spans="1:5" s="6" customFormat="1">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -1879,7 +1383,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:5">
+    <row r="24" spans="1:5" s="6" customFormat="1">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -1896,7 +1400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:5">
+    <row r="25" spans="1:5" s="6" customFormat="1">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -1913,7 +1417,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:5">
+    <row r="26" spans="1:5" s="6" customFormat="1">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -1930,20 +1434,20 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:5">
+    <row r="27" spans="1:5" s="6" customFormat="1">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="B27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1951,102 +1455,102 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:5">
+      <c r="B28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:5">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="6" customFormat="1">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:5">
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="6" customFormat="1">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="B31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>38</v>
+      <c r="D31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" t="s">
-        <v>39</v>
+      <c r="D32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" t="s">
-        <v>40</v>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2057,13 +1561,13 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2074,13 +1578,13 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2091,13 +1595,13 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2108,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2125,13 +1629,13 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2142,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2159,13 +1663,13 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2176,13 +1680,13 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2193,13 +1697,13 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2210,13 +1714,13 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2227,13 +1731,13 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2244,13 +1748,13 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2261,13 +1765,13 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2278,13 +1782,13 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D47" t="s">
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2295,50 +1799,50 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:5">
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="6" customFormat="1">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:5">
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="6" customFormat="1">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -2346,132 +1850,132 @@
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:5">
+      <c r="E51" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="6" customFormat="1">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>59</v>
+      <c r="B52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B53" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" spans="1:5">
+      <c r="B53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" spans="1:5">
+      <c r="B54" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" s="6" customFormat="1">
       <c r="A55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:5">
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="6" customFormat="1">
       <c r="A56" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="B56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>62</v>
+      <c r="D56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B57" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
-        <v>63</v>
+      <c r="D57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B58" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" t="s">
-        <v>62</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>64</v>
+      <c r="B58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2482,50 +1986,50 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
       </c>
       <c r="E59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="60" s="2" customFormat="1" spans="1:5">
-      <c r="A60" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" s="2" customFormat="1" spans="1:5">
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" s="6" customFormat="1">
       <c r="A61" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="1:5">
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>65</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" s="6" customFormat="1">
       <c r="A62" s="1" t="s">
         <v>5</v>
       </c>
@@ -2533,16 +2037,16 @@
         <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" spans="1:5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" s="6" customFormat="1">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -2550,16 +2054,16 @@
         <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" s="6" customFormat="1">
       <c r="A64" s="1" t="s">
         <v>5</v>
       </c>
@@ -2567,81 +2071,81 @@
         <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" s="6" customFormat="1">
       <c r="A65" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>71</v>
+      <c r="B65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B66" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" t="s">
-        <v>72</v>
+      <c r="B66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B67" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" t="s">
-        <v>73</v>
+      <c r="B67" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" t="s">
-        <v>71</v>
-      </c>
-      <c r="D68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" t="s">
-        <v>74</v>
+      <c r="B68" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2652,13 +2156,13 @@
         <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2669,80 +2173,80 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:5">
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="6" customFormat="1">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:5">
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" s="6" customFormat="1">
       <c r="A73" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" spans="1:5">
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>75</v>
+      </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" s="6" customFormat="1">
       <c r="A74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="B74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2750,16 +2254,16 @@
       <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B75" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" t="s">
-        <v>81</v>
-      </c>
-      <c r="D75" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="B75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="4" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2767,16 +2271,16 @@
       <c r="A76" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" t="s">
-        <v>81</v>
-      </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="B76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2784,17 +2288,17 @@
       <c r="A77" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B77" t="s">
-        <v>80</v>
-      </c>
-      <c r="C77" t="s">
-        <v>81</v>
-      </c>
-      <c r="D77" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="B77" s="1" t="s">
         <v>84</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2802,16 +2306,16 @@
         <v>5</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D78" t="s">
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2819,16 +2323,16 @@
         <v>5</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2836,16 +2340,16 @@
         <v>5</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2853,16 +2357,16 @@
         <v>5</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2870,16 +2374,16 @@
         <v>5</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2887,33 +2391,33 @@
         <v>5</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="1:5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>91</v>
+      <c r="B84" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" t="s">
+        <v>85</v>
+      </c>
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2921,16 +2425,16 @@
         <v>5</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2938,33 +2442,33 @@
         <v>5</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B87" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" t="s">
-        <v>92</v>
-      </c>
-      <c r="D87" t="s">
-        <v>27</v>
-      </c>
-      <c r="E87" t="s">
-        <v>93</v>
+      <c r="B87" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2972,33 +2476,33 @@
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D88" t="s">
         <v>8</v>
       </c>
       <c r="E88" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="1:5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>87</v>
+      <c r="B89" t="s">
+        <v>84</v>
+      </c>
+      <c r="C89" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3006,16 +2510,16 @@
         <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D90" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3023,33 +2527,33 @@
         <v>5</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E91" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B92" t="s">
-        <v>80</v>
-      </c>
-      <c r="C92" t="s">
-        <v>81</v>
-      </c>
-      <c r="D92" t="s">
-        <v>27</v>
-      </c>
-      <c r="E92" t="s">
-        <v>97</v>
+      <c r="B92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3057,16 +2561,16 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D93" t="s">
         <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3074,16 +2578,16 @@
         <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D94" t="s">
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3091,16 +2595,16 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D95" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E95" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3108,16 +2612,16 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3125,33 +2629,33 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C97" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D97" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="98" s="1" customFormat="1" spans="1:5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D98" s="1" t="s">
+      <c r="B98" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" t="s">
+        <v>98</v>
+      </c>
+      <c r="D98" t="s">
         <v>8</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>102</v>
+      <c r="E98" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3159,10 +2663,10 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
@@ -3176,33 +2680,33 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C100" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D100" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E100" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B101" t="s">
-        <v>80</v>
-      </c>
-      <c r="C101" t="s">
-        <v>94</v>
-      </c>
-      <c r="D101" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" t="s">
-        <v>103</v>
+      <c r="B101" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3210,16 +2714,16 @@
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D102" t="s">
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3227,16 +2731,16 @@
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D103" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E103" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3244,16 +2748,16 @@
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C104" t="s">
+        <v>98</v>
+      </c>
+      <c r="D104" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" t="s">
         <v>107</v>
-      </c>
-      <c r="D104" t="s">
-        <v>8</v>
-      </c>
-      <c r="E104" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3261,10 +2765,10 @@
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C105" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D105" t="s">
         <v>9</v>
@@ -3278,13 +2782,13 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C106" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="D106" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E106" t="s">
         <v>110</v>
@@ -3295,50 +2799,50 @@
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C107" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E107" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>84</v>
+      </c>
+      <c r="C108" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="108" s="2" customFormat="1" spans="1:5">
-      <c r="A108" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" spans="1:5">
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" s="6" customFormat="1">
       <c r="A109" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>113</v>
+      <c r="B109" t="s">
+        <v>84</v>
+      </c>
+      <c r="C109" t="s">
+        <v>111</v>
+      </c>
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3346,50 +2850,50 @@
         <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B111" t="s">
-        <v>80</v>
-      </c>
-      <c r="C111" t="s">
-        <v>107</v>
-      </c>
-      <c r="D111" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" t="s">
-        <v>115</v>
+      <c r="B111" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B112" t="s">
-        <v>80</v>
-      </c>
-      <c r="C112" t="s">
-        <v>107</v>
-      </c>
-      <c r="D112" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" t="s">
-        <v>116</v>
+      <c r="B112" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3397,13 +2901,13 @@
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D113" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
         <v>118</v>
@@ -3414,16 +2918,16 @@
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D114" t="s">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3431,16 +2935,16 @@
         <v>5</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D115" t="s">
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3448,16 +2952,16 @@
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D116" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3465,16 +2969,16 @@
         <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3482,16 +2986,16 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D118" t="s">
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3499,50 +3003,50 @@
         <v>5</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C119" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D119" t="s">
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="120" s="2" customFormat="1" spans="1:5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="121" s="1" customFormat="1" spans="1:5">
+      <c r="B120" t="s">
+        <v>121</v>
+      </c>
+      <c r="C120" t="s">
+        <v>122</v>
+      </c>
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" s="6" customFormat="1">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>89</v>
+      <c r="B121" t="s">
+        <v>121</v>
+      </c>
+      <c r="C121" t="s">
+        <v>122</v>
+      </c>
+      <c r="D121" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3550,50 +3054,50 @@
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C122" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D122" t="s">
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B123" t="s">
-        <v>117</v>
-      </c>
-      <c r="C123" t="s">
-        <v>118</v>
-      </c>
-      <c r="D123" t="s">
-        <v>27</v>
-      </c>
-      <c r="E123" t="s">
-        <v>120</v>
+      <c r="B123" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B124" t="s">
-        <v>117</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B124" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D124" t="s">
-        <v>8</v>
-      </c>
-      <c r="E124" t="s">
-        <v>121</v>
+      <c r="C124" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3601,16 +3105,16 @@
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C125" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3618,16 +3122,16 @@
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C126" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D126" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E126" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3635,16 +3139,16 @@
         <v>5</v>
       </c>
       <c r="B127" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C127" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D127" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E127" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3652,16 +3156,16 @@
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3669,16 +3173,16 @@
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C129" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3686,50 +3190,50 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C130" t="s">
+        <v>125</v>
+      </c>
+      <c r="D130" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>121</v>
+      </c>
+      <c r="C131" t="s">
+        <v>125</v>
+      </c>
+      <c r="D131" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" s="6" customFormat="1">
+      <c r="A132" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" t="s">
+        <v>121</v>
+      </c>
+      <c r="C132" t="s">
+        <v>125</v>
+      </c>
+      <c r="D132" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" t="s">
         <v>117</v>
-      </c>
-      <c r="C130" t="s">
-        <v>121</v>
-      </c>
-      <c r="D130" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="131" s="2" customFormat="1" spans="1:5">
-      <c r="A131" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="132" s="1" customFormat="1" spans="1:5">
-      <c r="A132" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3737,66 +3241,66 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C133" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D133" t="s">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B134" t="s">
-        <v>117</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="B134" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D134" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="C134" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="135" s="2" customFormat="1" spans="1:5">
+      <c r="D134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C135" s="2" t="s">
+      <c r="B135" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="1" spans="1:5">
+      <c r="C135" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" s="6" customFormat="1">
       <c r="A136" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="B136" t="s">
+        <v>121</v>
+      </c>
+      <c r="C136" t="s">
+        <v>125</v>
+      </c>
+      <c r="D136" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3805,50 +3309,50 @@
         <v>5</v>
       </c>
       <c r="B137" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C137" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D137" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E137" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="138" s="2" customFormat="1" spans="1:5">
+    <row r="138" spans="1:5">
       <c r="A138" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="139" s="1" customFormat="1" spans="1:5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" s="6" customFormat="1">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3856,50 +3360,50 @@
         <v>5</v>
       </c>
       <c r="B140" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C140" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E140" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="141" s="2" customFormat="1" spans="1:5">
-      <c r="A141" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="C141" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="142" s="1" customFormat="1" spans="1:5">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" s="6" customFormat="1">
       <c r="A142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3907,101 +3411,101 @@
         <v>5</v>
       </c>
       <c r="B143" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C143" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D143" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="144" s="2" customFormat="1" spans="1:5">
+    <row r="144" spans="1:5">
       <c r="A144" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="145" s="1" customFormat="1" spans="1:5">
+    <row r="145" spans="1:5" s="6" customFormat="1">
       <c r="A145" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B146" t="s">
-        <v>134</v>
-      </c>
-      <c r="C146" t="s">
-        <v>136</v>
-      </c>
-      <c r="D146" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="147" s="2" customFormat="1" spans="1:5">
+      <c r="B146" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="148" s="1" customFormat="1" spans="1:5">
+      <c r="B147" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" s="6" customFormat="1">
       <c r="A148" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4009,101 +3513,101 @@
         <v>5</v>
       </c>
       <c r="B149" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C149" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D149" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E149" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B150" t="s">
-        <v>134</v>
-      </c>
-      <c r="C150" t="s">
-        <v>136</v>
-      </c>
-      <c r="D150" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="151" s="2" customFormat="1" spans="1:5">
+      <c r="B150" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="2" t="s">
+      <c r="B151" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="C151" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" s="6" customFormat="1">
       <c r="A152" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B152" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C152" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D152" t="s">
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B153" t="s">
-        <v>134</v>
-      </c>
-      <c r="C153" t="s">
-        <v>136</v>
-      </c>
-      <c r="D153" t="s">
-        <v>27</v>
-      </c>
-      <c r="E153" t="s">
-        <v>141</v>
+      <c r="B153" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B154" t="s">
-        <v>134</v>
-      </c>
-      <c r="C154" t="s">
+      <c r="B154" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D154" t="s">
-        <v>27</v>
-      </c>
-      <c r="E154" t="s">
-        <v>143</v>
+      <c r="D154" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4111,13 +3615,13 @@
         <v>5</v>
       </c>
       <c r="B155" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C155" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D155" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>144</v>
@@ -4128,33 +3632,33 @@
         <v>5</v>
       </c>
       <c r="B156" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B157" t="s">
-        <v>134</v>
-      </c>
-      <c r="C157" t="s">
-        <v>144</v>
-      </c>
-      <c r="D157" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" t="s">
-        <v>130</v>
+      <c r="B157" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -4162,16 +3666,16 @@
         <v>5</v>
       </c>
       <c r="B158" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C158" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D158" t="s">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -4179,16 +3683,16 @@
         <v>5</v>
       </c>
       <c r="B159" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C159" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D159" t="s">
         <v>27</v>
       </c>
       <c r="E159" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4196,16 +3700,16 @@
         <v>5</v>
       </c>
       <c r="B160" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C160" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D160" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E160" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -4213,16 +3717,16 @@
         <v>5</v>
       </c>
       <c r="B161" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C161" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D161" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E161" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -4230,16 +3734,16 @@
         <v>5</v>
       </c>
       <c r="B162" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C162" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D162" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -4247,16 +3751,16 @@
         <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C163" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D163" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -4264,16 +3768,16 @@
         <v>5</v>
       </c>
       <c r="B164" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C164" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -4281,16 +3785,16 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C165" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D165" t="s">
         <v>27</v>
       </c>
       <c r="E165" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -4298,16 +3802,16 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C166" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D166" t="s">
         <v>8</v>
       </c>
       <c r="E166" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -4315,16 +3819,16 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C167" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D167" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E167" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4332,16 +3836,16 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C168" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D168" t="s">
         <v>27</v>
       </c>
       <c r="E168" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4349,16 +3853,16 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C169" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D169" t="s">
         <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4366,16 +3870,16 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C170" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4383,16 +3887,16 @@
         <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C171" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D171" t="s">
         <v>27</v>
       </c>
       <c r="E171" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4400,16 +3904,16 @@
         <v>5</v>
       </c>
       <c r="B172" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C172" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D172" t="s">
         <v>8</v>
       </c>
       <c r="E172" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4417,16 +3921,16 @@
         <v>5</v>
       </c>
       <c r="B173" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C173" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4434,16 +3938,16 @@
         <v>5</v>
       </c>
       <c r="B174" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C174" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D174" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E174" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4451,16 +3955,16 @@
         <v>5</v>
       </c>
       <c r="B175" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C175" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D175" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E175" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4468,16 +3972,16 @@
         <v>5</v>
       </c>
       <c r="B176" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C176" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="D176" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4485,16 +3989,16 @@
         <v>5</v>
       </c>
       <c r="B177" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C177" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="D177" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E177" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4502,16 +4006,16 @@
         <v>5</v>
       </c>
       <c r="B178" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C178" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="D178" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E178" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4519,16 +4023,16 @@
         <v>5</v>
       </c>
       <c r="B179" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C179" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4536,16 +4040,16 @@
         <v>5</v>
       </c>
       <c r="B180" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C180" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="D180" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E180" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4553,16 +4057,16 @@
         <v>5</v>
       </c>
       <c r="B181" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C181" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="D181" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E181" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4570,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="B182" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C182" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="D182" t="s">
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4587,16 +4091,16 @@
         <v>5</v>
       </c>
       <c r="B183" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C183" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="D183" t="s">
         <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4604,16 +4108,16 @@
         <v>5</v>
       </c>
       <c r="B184" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C184" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="D184" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E184" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4621,16 +4125,16 @@
         <v>5</v>
       </c>
       <c r="B185" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C185" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="D185" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E185" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4638,20 +4142,1431 @@
         <v>5</v>
       </c>
       <c r="B186" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C186" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="D186" t="s">
         <v>27</v>
       </c>
       <c r="E186" t="s">
-        <v>161</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B187" t="s">
+        <v>155</v>
+      </c>
+      <c r="C187" t="s">
+        <v>169</v>
+      </c>
+      <c r="D187" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B188" t="s">
+        <v>155</v>
+      </c>
+      <c r="C188" t="s">
+        <v>169</v>
+      </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B189" t="s">
+        <v>155</v>
+      </c>
+      <c r="C189" t="s">
+        <v>171</v>
+      </c>
+      <c r="D189" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B190" t="s">
+        <v>155</v>
+      </c>
+      <c r="C190" t="s">
+        <v>171</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B191" t="s">
+        <v>84</v>
+      </c>
+      <c r="C191" t="s">
+        <v>111</v>
+      </c>
+      <c r="D191" t="s">
+        <v>8</v>
+      </c>
+      <c r="E191" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B192" t="s">
+        <v>84</v>
+      </c>
+      <c r="C192" t="s">
+        <v>111</v>
+      </c>
+      <c r="D192" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B193" t="s">
+        <v>84</v>
+      </c>
+      <c r="C193" t="s">
+        <v>111</v>
+      </c>
+      <c r="D193" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B194" t="s">
+        <v>84</v>
+      </c>
+      <c r="C194" t="s">
+        <v>111</v>
+      </c>
+      <c r="D194" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B195" t="s">
+        <v>84</v>
+      </c>
+      <c r="C195" t="s">
+        <v>111</v>
+      </c>
+      <c r="D195" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B196" t="s">
+        <v>84</v>
+      </c>
+      <c r="C196" t="s">
+        <v>111</v>
+      </c>
+      <c r="D196" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B197" t="s">
+        <v>84</v>
+      </c>
+      <c r="C197" t="s">
+        <v>111</v>
+      </c>
+      <c r="D197" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B198" t="s">
+        <v>84</v>
+      </c>
+      <c r="C198" t="s">
+        <v>111</v>
+      </c>
+      <c r="D198" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B199" t="s">
+        <v>84</v>
+      </c>
+      <c r="C199" t="s">
+        <v>111</v>
+      </c>
+      <c r="D199" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B200" t="s">
+        <v>84</v>
+      </c>
+      <c r="C200" t="s">
+        <v>111</v>
+      </c>
+      <c r="D200" t="s">
+        <v>27</v>
+      </c>
+      <c r="E200" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B201" t="s">
+        <v>84</v>
+      </c>
+      <c r="C201" t="s">
+        <v>111</v>
+      </c>
+      <c r="D201" t="s">
+        <v>27</v>
+      </c>
+      <c r="E201" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B202" t="s">
+        <v>84</v>
+      </c>
+      <c r="C202" t="s">
+        <v>152</v>
+      </c>
+      <c r="D202" t="s">
+        <v>8</v>
+      </c>
+      <c r="E202" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B203" t="s">
+        <v>84</v>
+      </c>
+      <c r="C203" t="s">
+        <v>152</v>
+      </c>
+      <c r="D203" t="s">
+        <v>27</v>
+      </c>
+      <c r="E203" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B204" t="s">
+        <v>84</v>
+      </c>
+      <c r="C204" t="s">
+        <v>152</v>
+      </c>
+      <c r="D204" t="s">
+        <v>27</v>
+      </c>
+      <c r="E204" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B206" t="s">
+        <v>176</v>
+      </c>
+      <c r="C206" t="s">
+        <v>177</v>
+      </c>
+      <c r="D206" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B207" t="s">
+        <v>176</v>
+      </c>
+      <c r="C207" t="s">
+        <v>177</v>
+      </c>
+      <c r="D207" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B208" t="s">
+        <v>176</v>
+      </c>
+      <c r="C208" t="s">
+        <v>177</v>
+      </c>
+      <c r="D208" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B209" t="s">
+        <v>176</v>
+      </c>
+      <c r="C209" t="s">
+        <v>177</v>
+      </c>
+      <c r="D209" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B210" t="s">
+        <v>176</v>
+      </c>
+      <c r="C210" t="s">
+        <v>177</v>
+      </c>
+      <c r="D210" t="s">
+        <v>27</v>
+      </c>
+      <c r="E210" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B211" t="s">
+        <v>176</v>
+      </c>
+      <c r="C211" t="s">
+        <v>177</v>
+      </c>
+      <c r="D211" t="s">
+        <v>27</v>
+      </c>
+      <c r="E211" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B212" t="s">
+        <v>176</v>
+      </c>
+      <c r="C212" t="s">
+        <v>177</v>
+      </c>
+      <c r="D212" t="s">
+        <v>27</v>
+      </c>
+      <c r="E212" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B213" t="s">
+        <v>176</v>
+      </c>
+      <c r="C213" t="s">
+        <v>177</v>
+      </c>
+      <c r="D213" t="s">
+        <v>27</v>
+      </c>
+      <c r="E213" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B215" t="s">
+        <v>176</v>
+      </c>
+      <c r="C215" t="s">
+        <v>186</v>
+      </c>
+      <c r="D215" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B216" t="s">
+        <v>176</v>
+      </c>
+      <c r="C216" t="s">
+        <v>186</v>
+      </c>
+      <c r="D216" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B217" t="s">
+        <v>176</v>
+      </c>
+      <c r="C217" t="s">
+        <v>186</v>
+      </c>
+      <c r="D217" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B218" t="s">
+        <v>176</v>
+      </c>
+      <c r="C218" t="s">
+        <v>186</v>
+      </c>
+      <c r="D218" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B219" t="s">
+        <v>176</v>
+      </c>
+      <c r="C219" t="s">
+        <v>186</v>
+      </c>
+      <c r="D219" t="s">
+        <v>27</v>
+      </c>
+      <c r="E219" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B220" t="s">
+        <v>176</v>
+      </c>
+      <c r="C220" t="s">
+        <v>186</v>
+      </c>
+      <c r="D220" t="s">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B221" t="s">
+        <v>176</v>
+      </c>
+      <c r="C221" t="s">
+        <v>186</v>
+      </c>
+      <c r="D221" t="s">
+        <v>27</v>
+      </c>
+      <c r="E221" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B222" t="s">
+        <v>176</v>
+      </c>
+      <c r="C222" t="s">
+        <v>186</v>
+      </c>
+      <c r="D222" t="s">
+        <v>27</v>
+      </c>
+      <c r="E222" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B224" t="s">
+        <v>176</v>
+      </c>
+      <c r="C224" t="s">
+        <v>187</v>
+      </c>
+      <c r="D224" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B225" t="s">
+        <v>176</v>
+      </c>
+      <c r="C225" t="s">
+        <v>187</v>
+      </c>
+      <c r="D225" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B226" t="s">
+        <v>176</v>
+      </c>
+      <c r="C226" t="s">
+        <v>187</v>
+      </c>
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B227" t="s">
+        <v>176</v>
+      </c>
+      <c r="C227" t="s">
+        <v>187</v>
+      </c>
+      <c r="D227" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B228" t="s">
+        <v>176</v>
+      </c>
+      <c r="C228" t="s">
+        <v>187</v>
+      </c>
+      <c r="D228" t="s">
+        <v>27</v>
+      </c>
+      <c r="E228" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B229" t="s">
+        <v>176</v>
+      </c>
+      <c r="C229" t="s">
+        <v>187</v>
+      </c>
+      <c r="D229" t="s">
+        <v>27</v>
+      </c>
+      <c r="E229" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B230" t="s">
+        <v>176</v>
+      </c>
+      <c r="C230" t="s">
+        <v>187</v>
+      </c>
+      <c r="D230" t="s">
+        <v>27</v>
+      </c>
+      <c r="E230" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B231" t="s">
+        <v>176</v>
+      </c>
+      <c r="C231" t="s">
+        <v>187</v>
+      </c>
+      <c r="D231" t="s">
+        <v>27</v>
+      </c>
+      <c r="E231" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B233" t="s">
+        <v>188</v>
+      </c>
+      <c r="C233" t="s">
+        <v>188</v>
+      </c>
+      <c r="D233" t="s">
+        <v>27</v>
+      </c>
+      <c r="E233" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B234" t="s">
+        <v>188</v>
+      </c>
+      <c r="C234" t="s">
+        <v>188</v>
+      </c>
+      <c r="D234" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B235" t="s">
+        <v>188</v>
+      </c>
+      <c r="C235" t="s">
+        <v>188</v>
+      </c>
+      <c r="D235" t="s">
+        <v>27</v>
+      </c>
+      <c r="E235" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B236" t="s">
+        <v>188</v>
+      </c>
+      <c r="C236" t="s">
+        <v>188</v>
+      </c>
+      <c r="D236" t="s">
+        <v>27</v>
+      </c>
+      <c r="E236" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B237" t="s">
+        <v>188</v>
+      </c>
+      <c r="C237" t="s">
+        <v>188</v>
+      </c>
+      <c r="D237" t="s">
+        <v>27</v>
+      </c>
+      <c r="E237" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B238" t="s">
+        <v>188</v>
+      </c>
+      <c r="C238" t="s">
+        <v>188</v>
+      </c>
+      <c r="D238" t="s">
+        <v>27</v>
+      </c>
+      <c r="E238" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B239" t="s">
+        <v>188</v>
+      </c>
+      <c r="C239" t="s">
+        <v>188</v>
+      </c>
+      <c r="D239" t="s">
+        <v>27</v>
+      </c>
+      <c r="E239" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B241" t="s">
+        <v>196</v>
+      </c>
+      <c r="C241" t="s">
+        <v>177</v>
+      </c>
+      <c r="D241" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B242" t="s">
+        <v>196</v>
+      </c>
+      <c r="C242" t="s">
+        <v>177</v>
+      </c>
+      <c r="D242" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B243" t="s">
+        <v>196</v>
+      </c>
+      <c r="C243" t="s">
+        <v>177</v>
+      </c>
+      <c r="D243" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B244" t="s">
+        <v>196</v>
+      </c>
+      <c r="C244" t="s">
+        <v>177</v>
+      </c>
+      <c r="D244" t="s">
+        <v>9</v>
+      </c>
+      <c r="E244" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B245" t="s">
+        <v>196</v>
+      </c>
+      <c r="C245" t="s">
+        <v>177</v>
+      </c>
+      <c r="D245" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B246" t="s">
+        <v>196</v>
+      </c>
+      <c r="C246" t="s">
+        <v>177</v>
+      </c>
+      <c r="D246" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B247" t="s">
+        <v>196</v>
+      </c>
+      <c r="C247" t="s">
+        <v>177</v>
+      </c>
+      <c r="D247" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B248" t="s">
+        <v>196</v>
+      </c>
+      <c r="C248" t="s">
+        <v>177</v>
+      </c>
+      <c r="D248" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B249" t="s">
+        <v>196</v>
+      </c>
+      <c r="C249" t="s">
+        <v>177</v>
+      </c>
+      <c r="D249" t="s">
+        <v>27</v>
+      </c>
+      <c r="E249" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B251" t="s">
+        <v>196</v>
+      </c>
+      <c r="C251" t="s">
+        <v>186</v>
+      </c>
+      <c r="D251" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B252" t="s">
+        <v>196</v>
+      </c>
+      <c r="C252" t="s">
+        <v>186</v>
+      </c>
+      <c r="D252" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B253" t="s">
+        <v>196</v>
+      </c>
+      <c r="C253" t="s">
+        <v>186</v>
+      </c>
+      <c r="D253" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B254" t="s">
+        <v>196</v>
+      </c>
+      <c r="C254" t="s">
+        <v>186</v>
+      </c>
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B255" t="s">
+        <v>196</v>
+      </c>
+      <c r="C255" t="s">
+        <v>186</v>
+      </c>
+      <c r="D255" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B256" t="s">
+        <v>196</v>
+      </c>
+      <c r="C256" t="s">
+        <v>186</v>
+      </c>
+      <c r="D256" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B257" t="s">
+        <v>196</v>
+      </c>
+      <c r="C257" t="s">
+        <v>186</v>
+      </c>
+      <c r="D257" t="s">
+        <v>9</v>
+      </c>
+      <c r="E257" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B258" t="s">
+        <v>196</v>
+      </c>
+      <c r="C258" t="s">
+        <v>186</v>
+      </c>
+      <c r="D258" t="s">
+        <v>9</v>
+      </c>
+      <c r="E258" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B259" t="s">
+        <v>196</v>
+      </c>
+      <c r="C259" t="s">
+        <v>186</v>
+      </c>
+      <c r="D259" t="s">
+        <v>27</v>
+      </c>
+      <c r="E259" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B261" t="s">
+        <v>196</v>
+      </c>
+      <c r="C261" t="s">
+        <v>187</v>
+      </c>
+      <c r="D261" t="s">
+        <v>9</v>
+      </c>
+      <c r="E261" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B262" t="s">
+        <v>196</v>
+      </c>
+      <c r="C262" t="s">
+        <v>187</v>
+      </c>
+      <c r="D262" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B263" t="s">
+        <v>196</v>
+      </c>
+      <c r="C263" t="s">
+        <v>187</v>
+      </c>
+      <c r="D263" t="s">
+        <v>9</v>
+      </c>
+      <c r="E263" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B264" t="s">
+        <v>196</v>
+      </c>
+      <c r="C264" t="s">
+        <v>187</v>
+      </c>
+      <c r="D264" t="s">
+        <v>9</v>
+      </c>
+      <c r="E264" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B265" t="s">
+        <v>196</v>
+      </c>
+      <c r="C265" t="s">
+        <v>187</v>
+      </c>
+      <c r="D265" t="s">
+        <v>9</v>
+      </c>
+      <c r="E265" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B266" t="s">
+        <v>196</v>
+      </c>
+      <c r="C266" t="s">
+        <v>187</v>
+      </c>
+      <c r="D266" t="s">
+        <v>9</v>
+      </c>
+      <c r="E266" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B267" t="s">
+        <v>196</v>
+      </c>
+      <c r="C267" t="s">
+        <v>187</v>
+      </c>
+      <c r="D267" t="s">
+        <v>9</v>
+      </c>
+      <c r="E267" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B268" t="s">
+        <v>196</v>
+      </c>
+      <c r="C268" t="s">
+        <v>187</v>
+      </c>
+      <c r="D268" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B269" t="s">
+        <v>196</v>
+      </c>
+      <c r="C269" t="s">
+        <v>187</v>
+      </c>
+      <c r="D269" t="s">
+        <v>27</v>
+      </c>
+      <c r="E269" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E187" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Extraction/Master/standard_coa_master.xlsx
+++ b/Extraction/Master/standard_coa_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janarddanm\Downloads\01-09-2026\PFG_Extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4196E34-FBA0-469C-BD6F-CFC61906AE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB67EA94-78C3-46EF-B4B8-2995D5E88FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$187</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -82,9 +95,6 @@
     <t>Inventories</t>
   </si>
   <si>
-    <t>Prepaid items</t>
-  </si>
-  <si>
     <t>Restricted Assets - Current</t>
   </si>
   <si>
@@ -244,9 +254,6 @@
     <t>Total Liabilities and Net position</t>
   </si>
   <si>
-    <t>Total Liabilities, Deferred inflows of resources, and Net position</t>
-  </si>
-  <si>
     <t>Other Net Position</t>
   </si>
   <si>
@@ -641,6 +648,12 @@
   </si>
   <si>
     <t>Total long-term obligations</t>
+  </si>
+  <si>
+    <t>Total Liabilities, Deferred Inflows of Resources, and Net Position</t>
+  </si>
+  <si>
+    <t>Prepaid Items</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1002,7 @@
     <col min="2" max="2" width="25.5546875" customWidth="1"/>
     <col min="3" max="3" width="50.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.21875" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="5" max="5" width="55.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1193,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1210,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1227,7 +1240,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1244,7 +1257,7 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1261,7 +1274,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1278,7 +1291,7 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1295,7 +1308,7 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1312,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1326,10 +1339,10 @@
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
         <v>27</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="6" customFormat="1">
@@ -1343,10 +1356,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="6" customFormat="1">
@@ -1360,10 +1373,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="6" customFormat="1">
@@ -1377,10 +1390,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="6" customFormat="1">
@@ -1394,10 +1407,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="6" customFormat="1">
@@ -1411,10 +1424,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="6" customFormat="1">
@@ -1428,10 +1441,10 @@
         <v>7</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="6" customFormat="1">
@@ -1445,10 +1458,10 @@
         <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1456,16 +1469,16 @@
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1476,13 +1489,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="6" customFormat="1">
@@ -1493,13 +1506,13 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="6" customFormat="1">
@@ -1510,13 +1523,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1527,13 +1540,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1544,13 +1557,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1561,13 +1574,13 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
         <v>41</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1578,13 +1591,13 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1595,13 +1608,13 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1612,13 +1625,13 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1629,13 +1642,13 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1646,13 +1659,13 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1663,13 +1676,13 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1680,13 +1693,13 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1697,13 +1710,13 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1714,13 +1727,13 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1731,13 +1744,13 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" t="s">
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1748,13 +1761,13 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1765,13 +1778,13 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1782,13 +1795,13 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D47" t="s">
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1799,13 +1812,13 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1816,13 +1829,13 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="6" customFormat="1">
@@ -1833,13 +1846,13 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:5" s="6" customFormat="1">
@@ -1850,13 +1863,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:5" s="6" customFormat="1">
@@ -1867,13 +1880,13 @@
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1884,13 +1897,13 @@
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1901,13 +1914,13 @@
         <v>6</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:5" s="6" customFormat="1">
@@ -1918,13 +1931,13 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:5" s="6" customFormat="1">
@@ -1935,13 +1948,13 @@
         <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1952,13 +1965,13 @@
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1969,13 +1982,13 @@
         <v>6</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1986,13 +1999,13 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
         <v>65</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2003,13 +2016,13 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:5" s="6" customFormat="1">
@@ -2020,13 +2033,13 @@
         <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:5" s="6" customFormat="1">
@@ -2037,13 +2050,13 @@
         <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:5" s="6" customFormat="1">
@@ -2054,13 +2067,13 @@
         <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:5" s="6" customFormat="1">
@@ -2071,13 +2084,13 @@
         <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:5" s="6" customFormat="1">
@@ -2088,13 +2101,13 @@
         <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2105,13 +2118,13 @@
         <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
+      </c>
+      <c r="E66" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2119,16 +2132,16 @@
         <v>5</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2139,13 +2152,13 @@
         <v>6</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2156,13 +2169,13 @@
         <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2173,13 +2186,13 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
+        <v>73</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s">
         <v>75</v>
-      </c>
-      <c r="D70" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2190,13 +2203,13 @@
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:5" s="6" customFormat="1">
@@ -2207,13 +2220,13 @@
         <v>6</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D72" t="s">
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:5" s="6" customFormat="1">
@@ -2224,13 +2237,13 @@
         <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D73" t="s">
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:5" s="6" customFormat="1">
@@ -2241,13 +2254,13 @@
         <v>6</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2258,13 +2271,13 @@
         <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2275,13 +2288,13 @@
         <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2289,16 +2302,16 @@
         <v>5</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2306,16 +2319,16 @@
         <v>5</v>
       </c>
       <c r="B78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" t="s">
+        <v>83</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
         <v>84</v>
-      </c>
-      <c r="C78" t="s">
-        <v>85</v>
-      </c>
-      <c r="D78" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2323,16 +2336,16 @@
         <v>5</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
+        <v>83</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" t="s">
         <v>85</v>
-      </c>
-      <c r="D79" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2340,16 +2353,16 @@
         <v>5</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2357,16 +2370,16 @@
         <v>5</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2374,16 +2387,16 @@
         <v>5</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2391,16 +2404,16 @@
         <v>5</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2408,16 +2421,16 @@
         <v>5</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2425,16 +2438,16 @@
         <v>5</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2442,16 +2455,16 @@
         <v>5</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2459,16 +2472,16 @@
         <v>5</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2476,16 +2489,16 @@
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D88" t="s">
         <v>8</v>
       </c>
       <c r="E88" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2493,16 +2506,16 @@
         <v>5</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D89" t="s">
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2510,16 +2523,16 @@
         <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D90" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2527,16 +2540,16 @@
         <v>5</v>
       </c>
       <c r="B91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D91" t="s">
         <v>8</v>
       </c>
       <c r="E91" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2544,16 +2557,16 @@
         <v>5</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2561,16 +2574,16 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D93" t="s">
         <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2578,16 +2591,16 @@
         <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D94" t="s">
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2595,16 +2608,16 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2612,16 +2625,16 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D96" t="s">
         <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2629,16 +2642,16 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2646,16 +2659,16 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D98" t="s">
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2663,16 +2676,16 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C99" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
       </c>
       <c r="E99" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2680,16 +2693,16 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C100" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E100" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2697,16 +2710,16 @@
         <v>5</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2714,16 +2727,16 @@
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C102" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D102" t="s">
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2731,16 +2744,16 @@
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C103" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D103" t="s">
         <v>8</v>
       </c>
       <c r="E103" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2748,16 +2761,16 @@
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C104" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D104" t="s">
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2765,16 +2778,16 @@
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C105" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D105" t="s">
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2782,16 +2795,16 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C106" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D106" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E106" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2799,16 +2812,16 @@
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C107" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D107" t="s">
         <v>8</v>
       </c>
       <c r="E107" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2816,16 +2829,16 @@
         <v>5</v>
       </c>
       <c r="B108" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C108" t="s">
+        <v>109</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
         <v>111</v>
-      </c>
-      <c r="D108" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="109" spans="1:5" s="6" customFormat="1">
@@ -2833,16 +2846,16 @@
         <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C109" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2850,16 +2863,16 @@
         <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C110" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2867,16 +2880,16 @@
         <v>5</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2884,16 +2897,16 @@
         <v>5</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2901,16 +2914,16 @@
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C113" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D113" t="s">
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2918,16 +2931,16 @@
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C114" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D114" t="s">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2935,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="B115" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C115" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D115" t="s">
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2952,16 +2965,16 @@
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C116" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D116" t="s">
         <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2969,16 +2982,16 @@
         <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C117" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2986,16 +2999,16 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C118" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D118" t="s">
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3003,16 +3016,16 @@
         <v>5</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C119" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D119" t="s">
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3020,16 +3033,16 @@
         <v>5</v>
       </c>
       <c r="B120" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D120" t="s">
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121" spans="1:5" s="6" customFormat="1">
@@ -3037,16 +3050,16 @@
         <v>5</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D121" t="s">
         <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3054,16 +3067,16 @@
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C122" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D122" t="s">
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3071,16 +3084,16 @@
         <v>5</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3088,16 +3101,16 @@
         <v>5</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3105,16 +3118,16 @@
         <v>5</v>
       </c>
       <c r="B125" t="s">
+        <v>119</v>
+      </c>
+      <c r="C125" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" t="s">
         <v>121</v>
-      </c>
-      <c r="C125" t="s">
-        <v>122</v>
-      </c>
-      <c r="D125" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3122,16 +3135,16 @@
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C126" t="s">
+        <v>120</v>
+      </c>
+      <c r="D126" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" t="s">
         <v>122</v>
-      </c>
-      <c r="D126" t="s">
-        <v>27</v>
-      </c>
-      <c r="E126" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3139,16 +3152,16 @@
         <v>5</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C127" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
       </c>
       <c r="E127" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3156,16 +3169,16 @@
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C128" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3173,16 +3186,16 @@
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3190,16 +3203,16 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C130" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D130" t="s">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3207,16 +3220,16 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C131" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D131" t="s">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="132" spans="1:5" s="6" customFormat="1">
@@ -3224,16 +3237,16 @@
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C132" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D132" t="s">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3241,16 +3254,16 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C133" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D133" t="s">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3258,16 +3271,16 @@
         <v>5</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3275,16 +3288,16 @@
         <v>5</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="136" spans="1:5" s="6" customFormat="1">
@@ -3292,16 +3305,16 @@
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C136" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D136" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3309,16 +3322,16 @@
         <v>5</v>
       </c>
       <c r="B137" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C137" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D137" t="s">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3326,16 +3339,16 @@
         <v>5</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="139" spans="1:5" s="6" customFormat="1">
@@ -3343,16 +3356,16 @@
         <v>5</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3360,16 +3373,16 @@
         <v>5</v>
       </c>
       <c r="B140" t="s">
+        <v>129</v>
+      </c>
+      <c r="C140" t="s">
         <v>131</v>
-      </c>
-      <c r="C140" t="s">
-        <v>133</v>
       </c>
       <c r="D140" t="s">
         <v>8</v>
       </c>
       <c r="E140" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3377,16 +3390,16 @@
         <v>5</v>
       </c>
       <c r="B141" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D141" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="142" spans="1:5" s="6" customFormat="1">
@@ -3394,16 +3407,16 @@
         <v>5</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="D142" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3411,16 +3424,16 @@
         <v>5</v>
       </c>
       <c r="B143" t="s">
+        <v>129</v>
+      </c>
+      <c r="C143" t="s">
         <v>131</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" t="s">
         <v>133</v>
-      </c>
-      <c r="D143" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3428,16 +3441,16 @@
         <v>5</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D144" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="145" spans="1:5" s="6" customFormat="1">
@@ -3445,16 +3458,16 @@
         <v>5</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3462,16 +3475,16 @@
         <v>5</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3479,16 +3492,16 @@
         <v>5</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="148" spans="1:5" s="6" customFormat="1">
@@ -3496,16 +3509,16 @@
         <v>5</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3513,16 +3526,16 @@
         <v>5</v>
       </c>
       <c r="B149" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C149" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D149" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E149" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3530,16 +3543,16 @@
         <v>5</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3547,16 +3560,16 @@
         <v>5</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="D151" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="152" spans="1:5" s="6" customFormat="1">
@@ -3564,16 +3577,16 @@
         <v>5</v>
       </c>
       <c r="B152" t="s">
+        <v>138</v>
+      </c>
+      <c r="C152" t="s">
         <v>140</v>
       </c>
-      <c r="C152" t="s">
-        <v>142</v>
-      </c>
       <c r="D152" t="s">
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3581,16 +3594,16 @@
         <v>5</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D153" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3598,16 +3611,16 @@
         <v>5</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="D154" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3615,16 +3628,16 @@
         <v>5</v>
       </c>
       <c r="B155" t="s">
+        <v>138</v>
+      </c>
+      <c r="C155" t="s">
         <v>140</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
         <v>142</v>
-      </c>
-      <c r="D155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3632,16 +3645,16 @@
         <v>5</v>
       </c>
       <c r="B156" t="s">
+        <v>138</v>
+      </c>
+      <c r="C156" t="s">
         <v>140</v>
       </c>
-      <c r="C156" t="s">
-        <v>142</v>
-      </c>
       <c r="D156" t="s">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3649,16 +3662,16 @@
         <v>5</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3666,16 +3679,16 @@
         <v>5</v>
       </c>
       <c r="B158" t="s">
+        <v>138</v>
+      </c>
+      <c r="C158" t="s">
         <v>140</v>
       </c>
-      <c r="C158" t="s">
-        <v>142</v>
-      </c>
       <c r="D158" t="s">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3683,16 +3696,16 @@
         <v>5</v>
       </c>
       <c r="B159" t="s">
+        <v>138</v>
+      </c>
+      <c r="C159" t="s">
         <v>140</v>
       </c>
-      <c r="C159" t="s">
-        <v>142</v>
-      </c>
       <c r="D159" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E159" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3700,16 +3713,16 @@
         <v>5</v>
       </c>
       <c r="B160" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C160" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D160" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E160" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3717,16 +3730,16 @@
         <v>5</v>
       </c>
       <c r="B161" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C161" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D161" t="s">
         <v>8</v>
       </c>
       <c r="E161" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3734,16 +3747,16 @@
         <v>5</v>
       </c>
       <c r="B162" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C162" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3751,16 +3764,16 @@
         <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C163" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3768,16 +3781,16 @@
         <v>5</v>
       </c>
       <c r="B164" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C164" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3785,16 +3798,16 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C165" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E165" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3802,16 +3815,16 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C166" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D166" t="s">
         <v>8</v>
       </c>
       <c r="E166" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3819,16 +3832,16 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C167" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D167" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E167" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3836,16 +3849,16 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C168" t="s">
+        <v>150</v>
+      </c>
+      <c r="D168" t="s">
+        <v>26</v>
+      </c>
+      <c r="E168" t="s">
         <v>152</v>
-      </c>
-      <c r="D168" t="s">
-        <v>27</v>
-      </c>
-      <c r="E168" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3853,16 +3866,16 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C169" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D169" t="s">
         <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3870,16 +3883,16 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C170" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3887,16 +3900,16 @@
         <v>5</v>
       </c>
       <c r="B171" t="s">
+        <v>153</v>
+      </c>
+      <c r="C171" t="s">
+        <v>154</v>
+      </c>
+      <c r="D171" t="s">
+        <v>26</v>
+      </c>
+      <c r="E171" t="s">
         <v>155</v>
-      </c>
-      <c r="C171" t="s">
-        <v>156</v>
-      </c>
-      <c r="D171" t="s">
-        <v>27</v>
-      </c>
-      <c r="E171" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3904,16 +3917,16 @@
         <v>5</v>
       </c>
       <c r="B172" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C172" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D172" t="s">
         <v>8</v>
       </c>
       <c r="E172" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3921,16 +3934,16 @@
         <v>5</v>
       </c>
       <c r="B173" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C173" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3938,16 +3951,16 @@
         <v>5</v>
       </c>
       <c r="B174" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C174" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D174" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E174" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3955,16 +3968,16 @@
         <v>5</v>
       </c>
       <c r="B175" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C175" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D175" t="s">
         <v>8</v>
       </c>
       <c r="E175" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3972,16 +3985,16 @@
         <v>5</v>
       </c>
       <c r="B176" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C176" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D176" t="s">
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3989,16 +4002,16 @@
         <v>5</v>
       </c>
       <c r="B177" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C177" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D177" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E177" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4006,16 +4019,16 @@
         <v>5</v>
       </c>
       <c r="B178" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C178" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D178" t="s">
         <v>8</v>
       </c>
       <c r="E178" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4023,16 +4036,16 @@
         <v>5</v>
       </c>
       <c r="B179" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C179" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4040,16 +4053,16 @@
         <v>5</v>
       </c>
       <c r="B180" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C180" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D180" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E180" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4057,16 +4070,16 @@
         <v>5</v>
       </c>
       <c r="B181" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C181" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D181" t="s">
         <v>8</v>
       </c>
       <c r="E181" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4074,16 +4087,16 @@
         <v>5</v>
       </c>
       <c r="B182" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C182" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D182" t="s">
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4091,16 +4104,16 @@
         <v>5</v>
       </c>
       <c r="B183" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C183" t="s">
+        <v>162</v>
+      </c>
+      <c r="D183" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" t="s">
         <v>164</v>
-      </c>
-      <c r="D183" t="s">
-        <v>9</v>
-      </c>
-      <c r="E183" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4108,16 +4121,16 @@
         <v>5</v>
       </c>
       <c r="B184" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C184" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D184" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E184" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4125,16 +4138,16 @@
         <v>5</v>
       </c>
       <c r="B185" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C185" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D185" t="s">
         <v>8</v>
       </c>
       <c r="E185" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4142,16 +4155,16 @@
         <v>5</v>
       </c>
       <c r="B186" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C186" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D186" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E186" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4159,16 +4172,16 @@
         <v>5</v>
       </c>
       <c r="B187" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C187" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D187" t="s">
         <v>8</v>
       </c>
       <c r="E187" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4176,16 +4189,16 @@
         <v>5</v>
       </c>
       <c r="B188" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C188" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D188" t="s">
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4193,16 +4206,16 @@
         <v>5</v>
       </c>
       <c r="B189" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C189" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D189" t="s">
         <v>8</v>
       </c>
       <c r="E189" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4210,16 +4223,16 @@
         <v>5</v>
       </c>
       <c r="B190" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C190" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D190" t="s">
         <v>9</v>
       </c>
       <c r="E190" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4227,16 +4240,16 @@
         <v>5</v>
       </c>
       <c r="B191" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C191" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D191" t="s">
         <v>8</v>
       </c>
       <c r="E191" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4244,16 +4257,16 @@
         <v>5</v>
       </c>
       <c r="B192" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C192" t="s">
+        <v>109</v>
+      </c>
+      <c r="D192" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" t="s">
         <v>111</v>
-      </c>
-      <c r="D192" t="s">
-        <v>9</v>
-      </c>
-      <c r="E192" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4261,16 +4274,16 @@
         <v>5</v>
       </c>
       <c r="B193" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C193" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D193" t="s">
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4278,16 +4291,16 @@
         <v>5</v>
       </c>
       <c r="B194" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C194" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D194" t="s">
         <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4295,16 +4308,16 @@
         <v>5</v>
       </c>
       <c r="B195" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C195" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D195" t="s">
         <v>9</v>
       </c>
       <c r="E195" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4312,16 +4325,16 @@
         <v>5</v>
       </c>
       <c r="B196" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C196" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D196" t="s">
         <v>9</v>
       </c>
       <c r="E196" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4329,16 +4342,16 @@
         <v>5</v>
       </c>
       <c r="B197" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C197" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D197" t="s">
         <v>9</v>
       </c>
       <c r="E197" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4346,16 +4359,16 @@
         <v>5</v>
       </c>
       <c r="B198" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C198" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D198" t="s">
         <v>9</v>
       </c>
       <c r="E198" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4363,16 +4376,16 @@
         <v>5</v>
       </c>
       <c r="B199" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C199" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D199" t="s">
         <v>9</v>
       </c>
       <c r="E199" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4380,16 +4393,16 @@
         <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C200" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D200" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E200" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4397,16 +4410,16 @@
         <v>5</v>
       </c>
       <c r="B201" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C201" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D201" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E201" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4414,16 +4427,16 @@
         <v>5</v>
       </c>
       <c r="B202" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C202" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D202" t="s">
         <v>8</v>
       </c>
       <c r="E202" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4431,16 +4444,16 @@
         <v>5</v>
       </c>
       <c r="B203" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C203" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D203" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E203" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4448,16 +4461,16 @@
         <v>5</v>
       </c>
       <c r="B204" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C204" t="s">
+        <v>150</v>
+      </c>
+      <c r="D204" t="s">
+        <v>26</v>
+      </c>
+      <c r="E204" t="s">
         <v>152</v>
-      </c>
-      <c r="D204" t="s">
-        <v>27</v>
-      </c>
-      <c r="E204" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4465,16 +4478,16 @@
         <v>5</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4482,16 +4495,16 @@
         <v>5</v>
       </c>
       <c r="B206" t="s">
+        <v>174</v>
+      </c>
+      <c r="C206" t="s">
+        <v>175</v>
+      </c>
+      <c r="D206" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" t="s">
         <v>176</v>
-      </c>
-      <c r="C206" t="s">
-        <v>177</v>
-      </c>
-      <c r="D206" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4499,16 +4512,16 @@
         <v>5</v>
       </c>
       <c r="B207" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C207" t="s">
+        <v>175</v>
+      </c>
+      <c r="D207" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" t="s">
         <v>177</v>
-      </c>
-      <c r="D207" t="s">
-        <v>9</v>
-      </c>
-      <c r="E207" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4516,16 +4529,16 @@
         <v>5</v>
       </c>
       <c r="B208" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C208" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D208" t="s">
         <v>9</v>
       </c>
       <c r="E208" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4533,16 +4546,16 @@
         <v>5</v>
       </c>
       <c r="B209" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C209" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D209" t="s">
         <v>9</v>
       </c>
       <c r="E209" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4550,16 +4563,16 @@
         <v>5</v>
       </c>
       <c r="B210" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C210" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D210" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E210" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4567,16 +4580,16 @@
         <v>5</v>
       </c>
       <c r="B211" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C211" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D211" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E211" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4584,16 +4597,16 @@
         <v>5</v>
       </c>
       <c r="B212" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C212" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D212" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E212" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4601,16 +4614,16 @@
         <v>5</v>
       </c>
       <c r="B213" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C213" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D213" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E213" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4618,16 +4631,16 @@
         <v>5</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4635,16 +4648,16 @@
         <v>5</v>
       </c>
       <c r="B215" t="s">
+        <v>174</v>
+      </c>
+      <c r="C215" t="s">
+        <v>184</v>
+      </c>
+      <c r="D215" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" t="s">
         <v>176</v>
-      </c>
-      <c r="C215" t="s">
-        <v>186</v>
-      </c>
-      <c r="D215" t="s">
-        <v>9</v>
-      </c>
-      <c r="E215" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4652,16 +4665,16 @@
         <v>5</v>
       </c>
       <c r="B216" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C216" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D216" t="s">
         <v>9</v>
       </c>
       <c r="E216" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4669,16 +4682,16 @@
         <v>5</v>
       </c>
       <c r="B217" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C217" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D217" t="s">
         <v>9</v>
       </c>
       <c r="E217" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4686,16 +4699,16 @@
         <v>5</v>
       </c>
       <c r="B218" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C218" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D218" t="s">
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4703,16 +4716,16 @@
         <v>5</v>
       </c>
       <c r="B219" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C219" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D219" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E219" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4720,16 +4733,16 @@
         <v>5</v>
       </c>
       <c r="B220" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C220" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D220" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E220" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4737,16 +4750,16 @@
         <v>5</v>
       </c>
       <c r="B221" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C221" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D221" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E221" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4754,16 +4767,16 @@
         <v>5</v>
       </c>
       <c r="B222" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C222" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D222" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E222" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4771,16 +4784,16 @@
         <v>5</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4788,16 +4801,16 @@
         <v>5</v>
       </c>
       <c r="B224" t="s">
+        <v>174</v>
+      </c>
+      <c r="C224" t="s">
+        <v>185</v>
+      </c>
+      <c r="D224" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" t="s">
         <v>176</v>
-      </c>
-      <c r="C224" t="s">
-        <v>187</v>
-      </c>
-      <c r="D224" t="s">
-        <v>9</v>
-      </c>
-      <c r="E224" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4805,16 +4818,16 @@
         <v>5</v>
       </c>
       <c r="B225" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C225" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D225" t="s">
         <v>9</v>
       </c>
       <c r="E225" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4822,16 +4835,16 @@
         <v>5</v>
       </c>
       <c r="B226" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C226" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D226" t="s">
         <v>9</v>
       </c>
       <c r="E226" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4839,16 +4852,16 @@
         <v>5</v>
       </c>
       <c r="B227" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C227" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D227" t="s">
         <v>9</v>
       </c>
       <c r="E227" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4856,16 +4869,16 @@
         <v>5</v>
       </c>
       <c r="B228" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C228" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D228" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E228" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4873,16 +4886,16 @@
         <v>5</v>
       </c>
       <c r="B229" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C229" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D229" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E229" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4890,16 +4903,16 @@
         <v>5</v>
       </c>
       <c r="B230" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C230" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D230" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E230" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4907,16 +4920,16 @@
         <v>5</v>
       </c>
       <c r="B231" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C231" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D231" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E231" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4924,16 +4937,16 @@
         <v>5</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4941,16 +4954,16 @@
         <v>5</v>
       </c>
       <c r="B233" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C233" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D233" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E233" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4958,16 +4971,16 @@
         <v>5</v>
       </c>
       <c r="B234" t="s">
+        <v>186</v>
+      </c>
+      <c r="C234" t="s">
+        <v>186</v>
+      </c>
+      <c r="D234" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" t="s">
         <v>188</v>
-      </c>
-      <c r="C234" t="s">
-        <v>188</v>
-      </c>
-      <c r="D234" t="s">
-        <v>9</v>
-      </c>
-      <c r="E234" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4975,16 +4988,16 @@
         <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C235" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D235" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E235" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4992,16 +5005,16 @@
         <v>5</v>
       </c>
       <c r="B236" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C236" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D236" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E236" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5009,16 +5022,16 @@
         <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C237" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D237" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E237" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -5026,16 +5039,16 @@
         <v>5</v>
       </c>
       <c r="B238" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C238" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D238" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E238" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5043,16 +5056,16 @@
         <v>5</v>
       </c>
       <c r="B239" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C239" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D239" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E239" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5060,16 +5073,16 @@
         <v>5</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5077,16 +5090,16 @@
         <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C241" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D241" t="s">
         <v>9</v>
       </c>
       <c r="E241" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -5094,16 +5107,16 @@
         <v>5</v>
       </c>
       <c r="B242" t="s">
+        <v>194</v>
+      </c>
+      <c r="C242" t="s">
+        <v>175</v>
+      </c>
+      <c r="D242" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" t="s">
         <v>196</v>
-      </c>
-      <c r="C242" t="s">
-        <v>177</v>
-      </c>
-      <c r="D242" t="s">
-        <v>9</v>
-      </c>
-      <c r="E242" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5111,16 +5124,16 @@
         <v>5</v>
       </c>
       <c r="B243" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C243" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D243" t="s">
         <v>9</v>
       </c>
       <c r="E243" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -5128,16 +5141,16 @@
         <v>5</v>
       </c>
       <c r="B244" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C244" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D244" t="s">
         <v>9</v>
       </c>
       <c r="E244" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -5145,16 +5158,16 @@
         <v>5</v>
       </c>
       <c r="B245" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C245" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D245" t="s">
         <v>9</v>
       </c>
       <c r="E245" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -5162,16 +5175,16 @@
         <v>5</v>
       </c>
       <c r="B246" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C246" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D246" t="s">
         <v>9</v>
       </c>
       <c r="E246" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -5179,16 +5192,16 @@
         <v>5</v>
       </c>
       <c r="B247" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C247" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D247" t="s">
         <v>9</v>
       </c>
       <c r="E247" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -5196,16 +5209,16 @@
         <v>5</v>
       </c>
       <c r="B248" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C248" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D248" t="s">
         <v>9</v>
       </c>
       <c r="E248" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -5213,16 +5226,16 @@
         <v>5</v>
       </c>
       <c r="B249" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C249" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D249" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E249" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -5230,16 +5243,16 @@
         <v>5</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -5247,16 +5260,16 @@
         <v>5</v>
       </c>
       <c r="B251" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C251" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D251" t="s">
         <v>9</v>
       </c>
       <c r="E251" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -5264,16 +5277,16 @@
         <v>5</v>
       </c>
       <c r="B252" t="s">
+        <v>194</v>
+      </c>
+      <c r="C252" t="s">
+        <v>184</v>
+      </c>
+      <c r="D252" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" t="s">
         <v>196</v>
-      </c>
-      <c r="C252" t="s">
-        <v>186</v>
-      </c>
-      <c r="D252" t="s">
-        <v>9</v>
-      </c>
-      <c r="E252" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5281,16 +5294,16 @@
         <v>5</v>
       </c>
       <c r="B253" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C253" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D253" t="s">
         <v>9</v>
       </c>
       <c r="E253" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5298,16 +5311,16 @@
         <v>5</v>
       </c>
       <c r="B254" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C254" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D254" t="s">
         <v>9</v>
       </c>
       <c r="E254" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5315,16 +5328,16 @@
         <v>5</v>
       </c>
       <c r="B255" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C255" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D255" t="s">
         <v>9</v>
       </c>
       <c r="E255" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5332,16 +5345,16 @@
         <v>5</v>
       </c>
       <c r="B256" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C256" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D256" t="s">
         <v>9</v>
       </c>
       <c r="E256" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5349,16 +5362,16 @@
         <v>5</v>
       </c>
       <c r="B257" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C257" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D257" t="s">
         <v>9</v>
       </c>
       <c r="E257" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5366,16 +5379,16 @@
         <v>5</v>
       </c>
       <c r="B258" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C258" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D258" t="s">
         <v>9</v>
       </c>
       <c r="E258" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5383,16 +5396,16 @@
         <v>5</v>
       </c>
       <c r="B259" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C259" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D259" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E259" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5400,16 +5413,16 @@
         <v>5</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5417,16 +5430,16 @@
         <v>5</v>
       </c>
       <c r="B261" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C261" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D261" t="s">
         <v>9</v>
       </c>
       <c r="E261" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5434,16 +5447,16 @@
         <v>5</v>
       </c>
       <c r="B262" t="s">
+        <v>194</v>
+      </c>
+      <c r="C262" t="s">
+        <v>185</v>
+      </c>
+      <c r="D262" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262" t="s">
         <v>196</v>
-      </c>
-      <c r="C262" t="s">
-        <v>187</v>
-      </c>
-      <c r="D262" t="s">
-        <v>9</v>
-      </c>
-      <c r="E262" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5451,16 +5464,16 @@
         <v>5</v>
       </c>
       <c r="B263" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C263" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D263" t="s">
         <v>9</v>
       </c>
       <c r="E263" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5468,16 +5481,16 @@
         <v>5</v>
       </c>
       <c r="B264" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C264" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D264" t="s">
         <v>9</v>
       </c>
       <c r="E264" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5485,16 +5498,16 @@
         <v>5</v>
       </c>
       <c r="B265" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C265" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D265" t="s">
         <v>9</v>
       </c>
       <c r="E265" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5502,16 +5515,16 @@
         <v>5</v>
       </c>
       <c r="B266" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C266" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D266" t="s">
         <v>9</v>
       </c>
       <c r="E266" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5519,16 +5532,16 @@
         <v>5</v>
       </c>
       <c r="B267" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C267" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D267" t="s">
         <v>9</v>
       </c>
       <c r="E267" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5536,16 +5549,16 @@
         <v>5</v>
       </c>
       <c r="B268" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C268" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D268" t="s">
         <v>9</v>
       </c>
       <c r="E268" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5553,16 +5566,16 @@
         <v>5</v>
       </c>
       <c r="B269" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C269" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D269" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E269" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
